--- a/computer-science-math/resources/csm-p1-tracker-starter.xlsx
+++ b/computer-science-math/resources/csm-p1-tracker-starter.xlsx
@@ -8,12 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="READ ME FIRST" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Food Table" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Daily Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Dashboard" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sources" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Food Table" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Daily Log" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Weekly Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Dashboard" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Food Table'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Food Table'!$A$1:$G$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -53,7 +55,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +65,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="000E406A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E8F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBE7C6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7DDF2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7D6D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E4"/>
       </patternFill>
     </fill>
     <fill>
@@ -97,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -109,21 +141,40 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -132,6 +183,50 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D9E8F5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00DDEBD3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FBE7C6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E7DDF2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F7D6D0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E8E8E4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -493,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -527,55 +622,91 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>The Food Table headers and 15 starter foods with real, approximate macro values (add your own -- aim for 25+ by presentation day). The Daily Log headers, with a dropdown in the Food column pulled straight from your Food Table. The Dashboard layout, with labeled boxes waiting for your formulas.</t>
+          <t>The Sources tab (reference table + color key). The Food Table headers and 15 starter foods with real, approximate macro values and a Source for each (add your own -- aim for 25+ by presentation day). The Daily Log headers, with dropdowns in the Meal, Food, and Source columns. The Weekly Summary and Dashboard layouts, with labeled boxes waiting for your formulas.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>What you build</t>
+          <t>Source every number</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1) Grow the Food Table with foods you actually eat. 2) In the Daily Log, write the VLOOKUP formulas in the Calories/Protein/Carbs/Fat columns that look up each row's Food in the Food Table and multiply by Servings -- then keep logging real days. 3) In the Dashboard, write the SUMIF/AVERAGEIF formulas that summarize your log. 4) Build at least one honest chart from your own data (no answer charts are pre-built for you).</t>
+          <t>Every macro value you log must have a data origin, and you must record it in the Source column. The Sources tab lists the six accepted sources and the color that goes with each. Color-code every food's Source cell -- the color tells the reader how much to trust the number. A label beats an estimate.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>No answers here</t>
+          <t>What you build</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>There are no formulas hidden anywhere in this workbook. Every formula you see in your finished tracker will be one you wrote. If a cell looks empty, that's on purpose -- that's your work.</t>
+          <t>1) Grow the Food Table with foods you actually eat, each with its Source. 2) In the Daily Log, write VLOOKUP formulas that pull each row's Source and macros from the Food Table and multiply the macros by Servings. 3) In the Weekly Summary, write SUMIF/AVERAGEIF formulas that roll your log up by date. 4) In the Dashboard, summarize those daily figures and build at least one honest chart (no answer charts are pre-built for you).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Presentation date</t>
+          <t>Log 14 days</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Thursday, October 15 (Week 8 of the Year Calendar). Bring a working tracker and one real insight about your own eating patterns -- not just charts, an actual observation.</t>
+          <t>The cornerstone requires at least 14 days of your own logged food data. Start early -- you cannot cram two weeks of real eating in the last night.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>Two deliverables</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>1) The final spreadsheet (this workbook, completed). 2) A final presentation to the class: a working tracker plus one real insight about your own eating patterns -- not just charts, an actual observation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>No answers here</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>There are no formulas hidden anywhere in this workbook. Every formula you see in your finished tracker will be one you wrote. If a cell looks empty, that's on purpose -- that's your work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Presentation date</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Thursday, October 15 (Week 8 of the Year Calendar). Bring a working tracker and the insight you found in your own data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>Rubric</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Posted in the course Drive folder -- see the README's Google Drive link.</t>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>On the course kit page for this cornerstone (the same page linked from the class site) -- open the page and read it before you start building.</t>
         </is>
       </c>
     </row>
@@ -593,411 +724,180 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>Serving</t>
+          <t>What it's good for</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>Calories</t>
+          <t>Where to get it</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>Protein (g)</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Carbs (g)</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Fat (g)</t>
+          <t>Color</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Egg, large</t>
+          <t>MyFitnessPal</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>1 egg</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="n">
-        <v>72</v>
-      </c>
-      <c r="D2" s="6" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F2" s="6" t="n">
-        <v>4.8</v>
+          <t>App database; convenient, user-submitted values</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>myfitnesspal.com (or any food-logging app)</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>D9E8F5</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>White rice, cooked</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>1 cup</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="n">
-        <v>205</v>
-      </c>
-      <c r="D3" s="8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="F3" s="8" t="n">
-        <v>0.4</v>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>USDA FoodData Central</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Government reference; best for whole foods and basic ingredients</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>fdc.nal.usda.gov (downloadable datasets)</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>DDEBD3</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Chicken breast, grilled</t>
+          <t>Open Food Facts</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>100 g</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>165</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>3.6</v>
+          <t>Open, crowd-sourced; best for packaged and branded foods</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>world.openfoodfacts.org (CSV export)</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>FBE7C6</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Black beans, cooked</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>1 cup</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>227</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>0.9</v>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Manufacturer label</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>The package itself; authoritative for that exact product</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>the label on the product</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>E7DDF2</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Cafecito con azucar (Cuban coffee, sweet)</t>
+          <t>Restaurant nutrition</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>1 cup (8 oz)</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>1</v>
+          <t>Published by the restaurant; portions still vary</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>the restaurant's site or app</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>F7D6D0</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Plantain, fried (maduros)</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>1 cup</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>250</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>47</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>8.6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Ropa vieja (shredded beef)</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>1 cup</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>285</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Yuca con mojo</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>1 cup</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>220</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Avocado</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>1/2 fruit</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>160</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>14.7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Croqueta (ham)</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>1 piece</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>130</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Whole wheat bread</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>1 slice</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>81</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Greek yogurt, plain</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>1 cup (170 g)</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Banana</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>1 medium</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>105</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Pizza slice, cheese</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>1 slice</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="n">
-        <v>285</v>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>10.4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Cafe con leche</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>1 cup (8 oz)</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>110</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>5</v>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Estimate / other</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Your own call; flag it honestly</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>E8E8E4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Color-code every food's Source cell. The color tells the reader how much to trust the number -- a label beats an estimate.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F16"/>
+  <mergeCells count="1">
+    <mergeCell ref="A9:D9"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1008,147 +908,515 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>Meal</t>
+          <t>Serving</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>Calories</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>Servings</t>
+          <t>Protein (g)</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>Calories</t>
+          <t>Carbs (g)</t>
         </is>
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>Protein</t>
+          <t>Fat (g)</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
-          <t>Carbs</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Fat</t>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Breakfast</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Egg, large</t>
         </is>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>1 egg</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="n">
+        <v>72</v>
+      </c>
+      <c r="D2" s="14" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E2" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F2" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>USDA FoodData Central</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>White rice, cooked</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>1 cup</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="n">
+        <v>205</v>
+      </c>
+      <c r="D3" s="16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E3" s="16" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="F3" s="16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>USDA FoodData Central</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Chicken breast, grilled</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>100 g</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>165</v>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>USDA FoodData Central</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>Black beans, cooked</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>1 cup</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>227</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>USDA FoodData Central</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Cafecito con azucar (Cuban coffee, sweet)</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>1 cup (8 oz)</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>MyFitnessPal</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Plantain, fried (maduros)</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>1 cup</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>47</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>Restaurant nutrition</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Ropa vieja (shredded beef)</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>1 cup</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>285</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>Restaurant nutrition</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Yuca con mojo</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>1 cup</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>220</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>52</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>Restaurant nutrition</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Avocado</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>1/2 fruit</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>160</v>
+      </c>
+      <c r="D10" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Lunch</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>White rice, cooked</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Dinner</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Ropa vieja (shredded beef)</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-    </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Build it: in each Calories / Protein / Carbs / Fat cell above, write a VLOOKUP that finds this row's Food in the Food Table, then multiply by Servings. Once that works, keep logging your own real days starting row 7 -- the Food column dropdown pulls its list from your Food Table automatically.</t>
+      <c r="E10" s="14" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>USDA FoodData Central</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Croqueta (ham)</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>1 piece</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>130</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Open Food Facts</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Whole wheat bread</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>1 slice</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>81</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Manufacturer label</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Greek yogurt, plain</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>1 cup (170 g)</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>Open Food Facts</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>1 medium</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>105</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>USDA FoodData Central</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Pizza slice, cheese</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>1 slice</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>285</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>Restaurant nutrition</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Cafe con leche</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>1 cup (8 oz)</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>Estimate / other</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:H6"/>
-  </mergeCells>
+  <autoFilter ref="A1:G16"/>
+  <conditionalFormatting sqref="G2:G100">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$G2="MyFitnessPal"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>$G2="USDA FoodData Central"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>$G2="Open Food Facts"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="3">
+      <formula>$G2="Manufacturer label"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="4">
+      <formula>$G2="Restaurant nutrition"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="5">
+      <formula>$G2="Estimate / other"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="C2:C4 C7:C201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not in Food Table" error="Choose a food from the Food Table (or add it there first)." type="list">
-      <formula1>='Food Table'!$A$2:$A$16</formula1>
+    <dataValidation sqref="G2:G100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown source" error="Choose one of the six sources listed on the Sources tab." type="list">
+      <formula1>='Sources'!$A$2:$A$7</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1156,6 +1424,456 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Meal</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Servings</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Calories</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Protein (g)</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Carbs (g)</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Fat (g)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Egg, large</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="6" t="n"/>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="6" t="n"/>
+      <c r="H2" s="6" t="n"/>
+      <c r="I2" s="6" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>White rice, cooked</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n"/>
+      <c r="I3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Ropa vieja (shredded beef)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Build it: in each Calories / Protein / Carbs / Fat cell above, write a VLOOKUP that finds this row's Food in the Food Table, then multiply by Servings. The Source column is a second VLOOKUP -- return column 7 (the last column) instead of the macros. The Meal groups come from the old tracker template: Breakfast / Lunch / Dinner / Snacks. Once the lookups work, keep logging your own real days starting row 7.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:I6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E2:E201">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E2="MyFitnessPal"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>$E2="USDA FoodData Central"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>$E2="Open Food Facts"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="3">
+      <formula>$E2="Manufacturer label"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="4">
+      <formula>$E2="Restaurant nutrition"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="5">
+      <formula>$E2="Estimate / other"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation sqref="C2:C4 C7:C201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not in Food Table" error="Choose a food from the Food Table (or add it there first)." type="list">
+      <formula1>='Food Table'!$A$2:$A$100</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B4 B7:B201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown meal" error="Choose Breakfast, Lunch, Dinner, or Snacks." type="list">
+      <formula1>"Breakfast,Lunch,Dinner,Snacks"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E4 E7:E201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown source" error="Choose one of the six sources listed on the Sources tab." type="list">
+      <formula1>='Sources'!$A$2:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>This is the weekly roll-up from the old tracker template -- now it computes itself from your log with SUMIF. Each metric cell below should be a SUMIF keyed on the Daily Log Date column (and the Days logged column a COUNTIF), so adding log rows updates this tab automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Calories</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Protein (g)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Carbs (g)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Fat (g)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Days logged</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="14" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="14" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="n"/>
+      <c r="E7" s="14" t="n"/>
+      <c r="F7" s="14" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="14" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n"/>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
+      <c r="E9" s="14" t="n"/>
+      <c r="F9" s="14" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="14" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="14" t="n"/>
+      <c r="F14" s="14" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="14" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="14" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>TOTALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>Daily average</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="46" customHeight="1">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Hint: the per-day metric cells are blank -- they are yours to write. Calories average = AVERAGEIF over the date-keyed Daily Log rows. The TOTALS and Daily average rows are blank too: use SUM and AVERAGE of the 14 daily rows above.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1179,24 +1897,24 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>Daily Averages</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1208,10 +1926,10 @@
           <t>Average Calories / Day</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>&lt;- your AVERAGEIF formula goes here (Daily Log, matched by date)</t>
+      <c r="B5" s="6" t="n"/>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>&lt;- your AVERAGEIF formula goes here (Weekly Summary, keyed by date)</t>
         </is>
       </c>
     </row>
@@ -1221,10 +1939,10 @@
           <t>Average Protein (g) / Day</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>&lt;- your AVERAGEIF formula goes here (Daily Log, matched by date)</t>
+      <c r="B6" s="6" t="n"/>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>&lt;- your AVERAGEIF formula goes here (Weekly Summary, keyed by date)</t>
         </is>
       </c>
     </row>
@@ -1234,10 +1952,10 @@
           <t>Average Carbs (g) / Day</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>&lt;- your AVERAGEIF formula goes here (Daily Log, matched by date)</t>
+      <c r="B7" s="6" t="n"/>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>&lt;- your AVERAGEIF formula goes here (Weekly Summary, keyed by date)</t>
         </is>
       </c>
     </row>
@@ -1247,37 +1965,37 @@
           <t>Average Fat (g) / Day</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>&lt;- your AVERAGEIF formula goes here (Daily Log, matched by date)</t>
+      <c r="B8" s="6" t="n"/>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>&lt;- your AVERAGEIF formula goes here (Weekly Summary, keyed by date)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Target vs. Actual</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>Actual</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Difference</t>
         </is>
@@ -1289,9 +2007,9 @@
           <t>Calories</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1299,9 +2017,9 @@
           <t>Protein (g)</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1309,9 +2027,9 @@
           <t>Carbs (g)</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1319,26 +2037,26 @@
           <t>Fat (g)</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
     </row>
     <row r="16">
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>&lt;- Target: your own goal. Actual: pull from Daily Averages above.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>Chart</t>
         </is>
       </c>
     </row>
     <row r="19" ht="50" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>Insert your chart here: select A11:D15 (the Target vs. Actual table), then Insert &gt; Chart &gt; Clustered Column. Drag the chart into the empty space below this note.</t>
         </is>
